--- a/05_Figures/F05_classification/proteins/acute/HR_LR/spls/c_data/results.xlsx
+++ b/05_Figures/F05_classification/proteins/acute/HR_LR/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -134,25 +134,34 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">DUSP28</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPS20</t>
   </si>
   <si>
-    <t xml:space="preserve">DUSP28</t>
+    <t xml:space="preserve">AIMP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2</t>
   </si>
   <si>
     <t xml:space="preserve">MRPL47</t>
   </si>
   <si>
-    <t xml:space="preserve">AIMP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF2</t>
+    <t xml:space="preserve">PSMB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSCN1</t>
   </si>
   <si>
     <t xml:space="preserve">GLUL</t>
@@ -161,7 +170,7 @@
     <t xml:space="preserve">LAMTOR1</t>
   </si>
   <si>
-    <t xml:space="preserve">MAP1LC3B2</t>
+    <t xml:space="preserve">MYPN</t>
   </si>
   <si>
     <t xml:space="preserve">PANK4</t>
@@ -170,12 +179,15 @@
     <t xml:space="preserve">PBXIP1</t>
   </si>
   <si>
-    <t xml:space="preserve">PSMB2</t>
+    <t xml:space="preserve">PTPN1</t>
   </si>
   <si>
     <t xml:space="preserve">TOM1</t>
   </si>
   <si>
+    <t xml:space="preserve">UBE2M</t>
+  </si>
+  <si>
     <t xml:space="preserve">VARS1</t>
   </si>
   <si>
@@ -185,439 +197,466 @@
     <t xml:space="preserve">ENDOD1</t>
   </si>
   <si>
+    <t xml:space="preserve">GARNL3</t>
+  </si>
+  <si>
     <t xml:space="preserve">MLEC</t>
   </si>
   <si>
-    <t xml:space="preserve">MYPN</t>
+    <t xml:space="preserve">SUCLG2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYB5R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYSF</t>
   </si>
   <si>
     <t xml:space="preserve">PAFAH1B3</t>
   </si>
   <si>
-    <t xml:space="preserve">UBE2M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARNL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYB5R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FSCN1</t>
+    <t xml:space="preserve">STK38</t>
   </si>
   <si>
     <t xml:space="preserve">LZIC</t>
   </si>
   <si>
-    <t xml:space="preserve">PTPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUCLG2</t>
-  </si>
-  <si>
     <t xml:space="preserve">PSMA7</t>
   </si>
   <si>
+    <t xml:space="preserve">SELENBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNC45B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKCSH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAMPT</t>
+  </si>
+  <si>
     <t xml:space="preserve">RTN3</t>
   </si>
   <si>
-    <t xml:space="preserve">SELENBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCS</t>
+    <t xml:space="preserve">ALDH3A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCYL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1LI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALPK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1D</t>
   </si>
   <si>
     <t xml:space="preserve">HMGCL</t>
   </si>
   <si>
-    <t xml:space="preserve">PRKCSH</t>
+    <t xml:space="preserve">MAPRE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYLK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAFAH1B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNF123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5F1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CES2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1H1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHBP1L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNPDA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HADHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYO18A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7</t>
   </si>
   <si>
     <t xml:space="preserve">RWDD1</t>
   </si>
   <si>
-    <t xml:space="preserve">STK38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNC45B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH3A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAMPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALPK3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL6</t>
-  </si>
-  <si>
     <t xml:space="preserve">SCN1B</t>
   </si>
   <si>
-    <t xml:space="preserve">TMEM43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1LI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAFAH1B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCYL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APOO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF4</t>
+    <t xml:space="preserve">STT3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOLLIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHD14B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAD9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADH1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADSS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANKRD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APEH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF5</t>
   </si>
   <si>
     <t xml:space="preserve">ARHGAP19</t>
   </si>
   <si>
-    <t xml:space="preserve">CHCHD10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIC5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EHBP1L1</t>
+    <t xml:space="preserve">ARL6IP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLMH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11orf68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNA2D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHORDC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPNE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECI2</t>
   </si>
   <si>
     <t xml:space="preserve">EIF3E</t>
   </si>
   <si>
-    <t xml:space="preserve">GNPDA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYLK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYO18A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7</t>
+    <t xml:space="preserve">EPRS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSP90AB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYRM7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPKAPK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCTS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METTL26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTARC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTHFD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYLK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPLOC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTUB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PADI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKFB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGAM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM20D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3CB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRXL2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RANBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REEP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL13A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPLP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHOC2</t>
   </si>
   <si>
     <t xml:space="preserve">SMIM4</t>
   </si>
   <si>
-    <t xml:space="preserve">STT3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOLLIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPP2</t>
+    <t xml:space="preserve">STAT5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STOML2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TKFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXNRD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USP15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VPS35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDR1</t>
   </si>
   <si>
     <t xml:space="preserve">XRCC6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABHD14B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAD9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADH1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADSS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANKRD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APEH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5F1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLMH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLVRB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNA2D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CES2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPNE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DARS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPB41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HADHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HINT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HINT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSP90AB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCTS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METTL26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGLL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTARC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTHFD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPLOC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NQO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OTUB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PADI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRXL2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RANBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REEP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL13A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPLP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAT5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STOML2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIMM10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TKFC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXNRD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USP15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VPS35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDR1</t>
   </si>
 </sst>
 </file>
@@ -1004,19 +1043,19 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.392857142857143</v>
+        <v>0.410714285714286</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0462128719888035</v>
+        <v>0.06415416201817</v>
       </c>
       <c r="J2" t="n">
-        <v>0.739501413725482</v>
+        <v>0.757274409410401</v>
       </c>
       <c r="K2"/>
       <c r="L2"/>
@@ -1039,29 +1078,23 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.392857142857143</v>
+        <v>0.410714285714286</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0462128719888035</v>
+        <v>0.06415416201817</v>
       </c>
       <c r="J3" t="n">
-        <v>0.739501413725482</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.562189054726368</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.424285714285714</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.232423900781298</v>
-      </c>
+        <v>0.757274409410401</v>
+      </c>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1082,1606 +1115,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.535714285714286</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.660714285714286</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.267857142857143</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.571428571428572</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.196428571428571</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.607142857142857</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.446428571428571</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.196428571428571</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.0357142857142857</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.0892857142857143</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.142857142857143</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.285714285714286</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.142857142857143</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.428571428571429</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.714285714285714</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.107142857142857</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.410714285714286</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.339285714285714</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.607142857142857</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.0178571428571429</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.214285714285714</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.517857142857143</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.517857142857143</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.232142857142857</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.428571428571428</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.214285714285714</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0.0535714285714286</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0.678571428571429</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0.517857142857143</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0.214285714285714</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0.285714285714286</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0.696428571428571</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0.357142857142857</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0.892857142857143</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="n">
-        <v>0.517857142857143</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="n">
-        <v>0.714285714285714</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="n">
-        <v>0.535714285714286</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="n">
-        <v>0.303571428571429</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="n">
-        <v>0.321428571428571</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="n">
-        <v>0.392857142857143</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="n">
-        <v>0.357142857142857</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0.321428571428571</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="n">
-        <v>0.446428571428571</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="n">
-        <v>0.428571428571429</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="n">
-        <v>0.392857142857143</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="n">
-        <v>0.571428571428571</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="n">
-        <v>0.642857142857143</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="n">
-        <v>0.0892857142857143</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="n">
-        <v>0.678571428571429</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="n">
-        <v>0.214285714285714</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="n">
-        <v>0.0892857142857143</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="n">
-        <v>0.839285714285714</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="n">
-        <v>0.607142857142857</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="n">
-        <v>0.482142857142857</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="n">
-        <v>0.107142857142857</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="n">
-        <v>0.553571428571429</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="n">
-        <v>0.142857142857143</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="n">
-        <v>0.303571428571429</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="n">
-        <v>0.0178571428571429</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="n">
-        <v>0.482142857142857</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="n">
-        <v>0.464285714285714</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="n">
-        <v>0.839285714285714</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="n">
-        <v>0.553571428571429</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="n">
-        <v>0.982142857142857</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="n">
-        <v>0.607142857142857</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="n">
-        <v>0.607142857142857</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="n">
-        <v>0.428571428571428</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="n">
-        <v>0.196428571428571</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="n">
-        <v>0.803571428571429</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="n">
-        <v>0.178571428571429</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="n">
-        <v>0.517857142857143</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="n">
-        <v>0.339285714285714</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="n">
-        <v>0.464285714285714</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="n">
-        <v>0.803571428571429</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="n">
-        <v>0.892857142857143</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="n">
-        <v>0.392857142857143</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="n">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="n">
-        <v>0.107142857142857</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="n">
-        <v>0.160714285714286</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="n">
-        <v>0.642857142857143</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="n">
-        <v>0.464285714285714</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="n">
-        <v>0.0892857142857143</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="n">
-        <v>0.660714285714286</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="n">
-        <v>0.821428571428571</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="n">
-        <v>0.571428571428571</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="n">
-        <v>0.232142857142857</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="n">
-        <v>0.446428571428571</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="n">
-        <v>0.642857142857143</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="n">
-        <v>0.357142857142857</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="n">
-        <v>0.107142857142857</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="n">
-        <v>0.535714285714286</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="n">
-        <v>0.535714285714286</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="n">
-        <v>0.517857142857143</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="n">
-        <v>0.232142857142857</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="n">
-        <v>0.642857142857143</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="n">
-        <v>0.428571428571428</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="n">
-        <v>0.446428571428571</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="n">
-        <v>0.696428571428572</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="n">
-        <v>0.0535714285714286</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="n">
-        <v>0.303571428571429</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="n">
-        <v>0.446428571428571</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="n">
-        <v>0.142857142857143</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="n">
-        <v>0.696428571428571</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="n">
-        <v>0.339285714285714</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="n">
-        <v>0.821428571428572</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="n">
-        <v>0.446428571428571</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="n">
-        <v>0.714285714285714</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="n">
-        <v>0.214285714285714</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="n">
-        <v>0.0357142857142857</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="n">
-        <v>0.553571428571428</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="n">
-        <v>0.321428571428571</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="n">
-        <v>0.232142857142857</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="n">
-        <v>0.517857142857143</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="n">
-        <v>0.0178571428571429</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="n">
-        <v>0.107142857142857</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="n">
-        <v>0.339285714285714</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="n">
-        <v>0.392857142857143</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="n">
-        <v>0.839285714285714</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="n">
-        <v>0.410714285714286</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="n">
-        <v>0.339285714285714</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="n">
-        <v>0.535714285714286</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="n">
-        <v>0.410714285714286</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="n">
-        <v>0.321428571428571</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="n">
-        <v>0.232142857142857</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="n">
-        <v>0.357142857142857</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="n">
-        <v>0.428571428571428</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="n">
-        <v>0.0892857142857143</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="n">
-        <v>0.607142857142857</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="n">
-        <v>0.857142857142857</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="n">
-        <v>0.142857142857143</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="n">
-        <v>0.321428571428571</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="n">
-        <v>0.767857142857143</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="n">
-        <v>0.428571428571429</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="n">
-        <v>0.392857142857143</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="n">
-        <v>0.303571428571429</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="n">
-        <v>0.696428571428572</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="n">
-        <v>0.553571428571429</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="n">
-        <v>0.392857142857143</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="n">
-        <v>0.357142857142857</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="n">
-        <v>0.678571428571429</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="n">
-        <v>0.464285714285714</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="n">
-        <v>0.803571428571429</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="n">
-        <v>0.0178571428571429</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="n">
-        <v>0.285714285714286</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="n">
-        <v>0.839285714285714</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="n">
-        <v>0.446428571428571</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="n">
-        <v>0.285714285714286</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="n">
-        <v>0.321428571428571</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="n">
-        <v>0.267857142857143</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="n">
-        <v>0.267857142857143</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="n">
-        <v>0.428571428571428</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="n">
-        <v>0.517857142857143</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="n">
-        <v>0.678571428571429</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="n">
-        <v>0.642857142857143</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="n">
-        <v>0.410714285714286</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="n">
-        <v>0.392857142857143</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="n">
-        <v>0.446428571428571</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="n">
-        <v>0.285714285714286</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="n">
-        <v>0.428571428571428</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="n">
-        <v>0.464285714285714</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="n">
-        <v>0.803571428571429</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="n">
-        <v>0.678571428571428</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="n">
-        <v>0.267857142857143</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="n">
-        <v>0.303571428571429</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="n">
-        <v>0.714285714285714</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="n">
-        <v>0.589285714285714</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="n">
-        <v>0.607142857142857</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="n">
-        <v>0.928571428571428</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="n">
-        <v>0.285714285714286</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="n">
-        <v>0.357142857142857</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="n">
-        <v>0.142857142857143</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="n">
-        <v>0.303571428571429</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="n">
-        <v>0.678571428571428</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="n">
-        <v>0.732142857142857</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -2718,7 +1151,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.855597359719022</v>
+        <v>0.846252780904875</v>
       </c>
     </row>
     <row r="3">
@@ -2732,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.51187124204492</v>
+        <v>0.510361931032485</v>
       </c>
     </row>
     <row r="4">
@@ -2746,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.280378400247841</v>
+        <v>0.264720495957557</v>
       </c>
     </row>
     <row r="5">
@@ -2760,7 +1193,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.277443367203063</v>
+        <v>0.257148569790954</v>
       </c>
     </row>
     <row r="6">
@@ -2774,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.16473294747226</v>
+        <v>2.16521906572763</v>
       </c>
     </row>
     <row r="7">
@@ -2788,7 +1221,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.280719842595125</v>
+        <v>0.34062699498389</v>
       </c>
     </row>
     <row r="8">
@@ -2802,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0205135715913812</v>
+        <v>0.0188505555188161</v>
       </c>
     </row>
     <row r="9">
@@ -2816,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.630578273275359</v>
+        <v>0.673759981121251</v>
       </c>
     </row>
     <row r="10">
@@ -2830,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.236551049916146</v>
+        <v>0.237973258562443</v>
       </c>
     </row>
     <row r="11">
@@ -2844,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.648342624047529</v>
+        <v>0.429478465957791</v>
       </c>
     </row>
     <row r="12">
@@ -2858,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.368972223602465</v>
+        <v>0.375173190323808</v>
       </c>
     </row>
     <row r="13">
@@ -2872,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.53817088178966</v>
+        <v>0.513609863532644</v>
       </c>
     </row>
     <row r="14">
@@ -2886,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.645344061795686</v>
+        <v>0.659871409149779</v>
       </c>
     </row>
     <row r="15">
@@ -2900,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.592862473965033</v>
+        <v>0.589128435924708</v>
       </c>
     </row>
     <row r="16">
@@ -2914,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.444030058399608</v>
+        <v>0.456062025220912</v>
       </c>
     </row>
   </sheetData>
@@ -2964,10 +1397,10 @@
         <v>40</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.933333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2992,10 +1425,10 @@
         <v>42</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3006,10 +1439,10 @@
         <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3020,10 +1453,10 @@
         <v>44</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3034,10 +1467,10 @@
         <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3048,10 +1481,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3062,10 +1495,10 @@
         <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3076,10 +1509,10 @@
         <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3090,10 +1523,10 @@
         <v>49</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -3104,10 +1537,10 @@
         <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -3118,10 +1551,10 @@
         <v>51</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3132,10 +1565,10 @@
         <v>52</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -3146,10 +1579,10 @@
         <v>53</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -3160,10 +1593,10 @@
         <v>54</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>0.733333333333333</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -3174,10 +1607,10 @@
         <v>55</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>0.733333333333333</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="19">
@@ -3188,10 +1621,10 @@
         <v>56</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>0.733333333333333</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -3202,10 +1635,10 @@
         <v>57</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>0.733333333333333</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="21">
@@ -3216,10 +1649,10 @@
         <v>58</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22">
@@ -3230,10 +1663,10 @@
         <v>59</v>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23">
@@ -3244,10 +1677,10 @@
         <v>60</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>0.666666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
@@ -3258,10 +1691,10 @@
         <v>61</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>0.666666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25">
@@ -3272,10 +1705,10 @@
         <v>62</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -3286,10 +1719,10 @@
         <v>63</v>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -3300,10 +1733,10 @@
         <v>64</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -3314,10 +1747,10 @@
         <v>65</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -3328,10 +1761,10 @@
         <v>66</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -3342,10 +1775,10 @@
         <v>67</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>0.533333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="31">
@@ -3356,10 +1789,10 @@
         <v>68</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="32">
@@ -3370,10 +1803,10 @@
         <v>69</v>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="33">
@@ -3384,10 +1817,10 @@
         <v>70</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.466666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="34">
@@ -3398,10 +1831,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>0.466666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="35">
@@ -3412,10 +1845,10 @@
         <v>72</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="36">
@@ -3426,10 +1859,10 @@
         <v>73</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="37">
@@ -3440,10 +1873,10 @@
         <v>74</v>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="38">
@@ -3454,10 +1887,10 @@
         <v>75</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="39">
@@ -3468,10 +1901,10 @@
         <v>76</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="40">
@@ -3482,10 +1915,10 @@
         <v>77</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="41">
@@ -3496,10 +1929,10 @@
         <v>78</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42">
@@ -3594,10 +2027,10 @@
         <v>85</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="49">
@@ -3608,10 +2041,10 @@
         <v>86</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -3622,10 +2055,10 @@
         <v>87</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="51">
@@ -3636,10 +2069,10 @@
         <v>88</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="52">
@@ -3734,10 +2167,10 @@
         <v>95</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="59">
@@ -3748,10 +2181,10 @@
         <v>96</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="60">
@@ -3762,10 +2195,10 @@
         <v>97</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="61">
@@ -3776,10 +2209,10 @@
         <v>98</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="62">
@@ -3790,10 +2223,10 @@
         <v>99</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="63">
@@ -4056,10 +2489,10 @@
         <v>118</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="82">
@@ -4070,10 +2503,10 @@
         <v>119</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="83">
@@ -4084,10 +2517,10 @@
         <v>120</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="84">
@@ -4098,10 +2531,10 @@
         <v>121</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="85">
@@ -4112,10 +2545,10 @@
         <v>122</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="86">
@@ -4126,10 +2559,10 @@
         <v>123</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="87">
@@ -5207,6 +3640,188 @@
         <v>1</v>
       </c>
       <c r="D163" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>201</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>202</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>203</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>204</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>205</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>206</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>207</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>208</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>209</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>210</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>211</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>212</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>213</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F05_classification/proteins/acute/HR_LR/spls/c_data/results.xlsx
+++ b/05_Figures/F05_classification/proteins/acute/HR_LR/spls/c_data/results.xlsx
@@ -1081,7 +1081,7 @@
         <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0.410714285714286</v>
@@ -1092,9 +1092,15 @@
       <c r="J3" t="n">
         <v>0.757274409410401</v>
       </c>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="K3" t="n">
+        <v>0.552238805970149</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.434821428571429</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.237035321776882</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1115,6 +1121,1606 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.553571428571429</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.714285714285714</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.321428571428571</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.553571428571429</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.214285714285714</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.535714285714286</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.446428571428571</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.107142857142857</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0892857142857143</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0892857142857143</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.285714285714286</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.303571428571429</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0535714285714286</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.732142857142857</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.107142857142857</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.410714285714286</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.232142857142857</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.178571428571429</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.517857142857143</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.303571428571428</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.446428571428571</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.267857142857143</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.285714285714286</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.107142857142857</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.660714285714286</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.464285714285714</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.267857142857143</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.357142857142857</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.696428571428571</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.410714285714286</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.839285714285714</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.678571428571429</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0.535714285714286</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0.285714285714286</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.446428571428571</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.339285714285714</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.285714285714286</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.357142857142857</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.285714285714286</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0.303571428571429</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0.428571428571428</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.553571428571429</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.428571428571429</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.428571428571428</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.321428571428571</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0.607142857142857</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0.589285714285714</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0.0892857142857143</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0.696428571428572</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0.660714285714286</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0.678571428571428</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0.0892857142857143</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.303571428571429</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.0535714285714286</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.107142857142857</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0.303571428571429</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.714285714285714</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="n">
+        <v>0.482142857142857</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="n">
+        <v>0.214285714285714</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0.803571428571428</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.589285714285714</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0.785714285714286</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.982142857142857</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.589285714285714</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.482142857142857</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.214285714285714</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0.839285714285714</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.160714285714286</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0.714285714285714</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0.482142857142857</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0.392857142857143</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0.714285714285714</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0.946428571428571</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0.410714285714286</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0.107142857142857</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0.642857142857143</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0.428571428571428</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0.0178571428571429</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0.821428571428571</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.178571428571429</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="n">
+        <v>0.446428571428571</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0.660714285714286</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0.321428571428571</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.0892857142857143</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="n">
+        <v>0.446428571428571</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0.214285714285714</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0.517857142857143</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.535714285714286</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0.196428571428571</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0.642857142857143</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0.392857142857143</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="n">
+        <v>0.410714285714286</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0.696428571428571</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.0178571428571429</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.267857142857143</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.464285714285714</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.196428571428571</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.732142857142857</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.339285714285714</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.857142857142857</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.732142857142857</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.785714285714286</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.482142857142857</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.678571428571429</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.285714285714286</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.0357142857142857</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.339285714285714</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.214285714285714</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.446428571428571</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.0892857142857143</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.357142857142857</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.464285714285714</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.839285714285714</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.339285714285714</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.339285714285714</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.464285714285714</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.446428571428571</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.410714285714286</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0.321428571428571</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0.196428571428571</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0.357142857142857</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="n">
+        <v>0.464285714285714</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="n">
+        <v>0.107142857142857</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0.607142857142857</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0.892857142857143</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.482142857142857</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0.714285714285714</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="n">
+        <v>0.339285714285714</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0.392857142857143</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0.732142857142857</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0.428571428571429</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0.357142857142857</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0.660714285714286</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0.464285714285714</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="n">
+        <v>0.821428571428571</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0.196428571428571</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0.642857142857143</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0.267857142857143</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0.839285714285714</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0.428571428571428</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="n">
+        <v>0.214285714285714</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0.303571428571429</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="n">
+        <v>0.196428571428571</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="n">
+        <v>0.267857142857143</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0.446428571428571</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0.428571428571428</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="n">
+        <v>0.571428571428572</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="n">
+        <v>0.160714285714286</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="n">
+        <v>0.410714285714286</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="n">
+        <v>0.803571428571428</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="n">
+        <v>0.446428571428571</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="n">
+        <v>0.339285714285714</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="n">
+        <v>0.714285714285714</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="n">
+        <v>0.767857142857143</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="n">
+        <v>0.714285714285714</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="n">
+        <v>0.285714285714286</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="n">
+        <v>0.857142857142857</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="n">
+        <v>0.267857142857143</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="n">
+        <v>0.714285714285714</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="n">
+        <v>0.696428571428571</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="n">
+        <v>0.464285714285714</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="n">
+        <v>0.857142857142857</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="n">
+        <v>0.339285714285714</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="n">
+        <v>0.285714285714286</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="n">
+        <v>0.303571428571429</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="n">
+        <v>0.660714285714286</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="n">
+        <v>0.767857142857143</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
